--- a/ig/DM-AVRIL-2026/ValueSet-JDV-J01-XdsAuthorSpecialty-CISIS.xlsx
+++ b/ig/DM-AVRIL-2026/ValueSet-JDV-J01-XdsAuthorSpecialty-CISIS.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="821">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="829">
   <si>
     <t>Property</t>
   </si>
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20260505120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00+01:00</t>
+    <t>2026-05-05T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2477,6 +2477,30 @@
   </si>
   <si>
     <t>Conseiller conjugal et familial</t>
+  </si>
+  <si>
+    <t>376</t>
+  </si>
+  <si>
+    <t>PADHUE - Médecin</t>
+  </si>
+  <si>
+    <t>377</t>
+  </si>
+  <si>
+    <t>PADHUE - Pharmacien</t>
+  </si>
+  <si>
+    <t>378</t>
+  </si>
+  <si>
+    <t>PADHUE - Sage Femme</t>
+  </si>
+  <si>
+    <t>379</t>
+  </si>
+  <si>
+    <t>PADHUE - Chirurgien Dentiste</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R85-RolePriseCharge/FHIR/TRE-R85-RolePriseCharge</t>
@@ -5469,7 +5493,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B74"/>
+  <dimension ref="A1:B78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -6054,18 +6078,50 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>42</v>
+        <v>820</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>42</v>
+        <v>821</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
+        <v>822</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>826</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
         <v>43</v>
       </c>
-      <c r="B74" t="s" s="2">
-        <v>820</v>
+      <c r="B78" t="s" s="2">
+        <v>828</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-AVRIL-2026/ValueSet-JDV-J01-XdsAuthorSpecialty-CISIS.xlsx
+++ b/ig/DM-AVRIL-2026/ValueSet-JDV-J01-XdsAuthorSpecialty-CISIS.xlsx
@@ -2158,7 +2158,7 @@
     <t>317</t>
   </si>
   <si>
-    <t>Préparateur en pharmacie (officine)</t>
+    <t>Préparateur en pharmacie</t>
   </si>
   <si>
     <t>319</t>
